--- a/AI Fluency/Week 1/Table.xlsx
+++ b/AI Fluency/Week 1/Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brady\Documents\GitHub\FlyRankAI\AI Fluency\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brady\Documents\GitHub\FlyRankAI\AI Fluency\Week 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D6715E0-C70F-4976-B28A-F2EB252BB166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6398034D-8EB5-4582-92AE-6CA62B367200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{137620F6-6144-4B7C-8D4D-1C9773198FD2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Delegate to AI with review</t>
   </si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t>Respond to the question teammate always asks. (I can create an AI agent to help answer repeated questions.)</t>
+  </si>
+  <si>
+    <t>1 Respond to the question teammate always asks. An AI agent that will answer the any basic question, so that I won't need to waste my time.</t>
+  </si>
+  <si>
+    <t>2. Studying after class. Create an AI scan my notes and any relevant documents, and create a review document.</t>
+  </si>
+  <si>
+    <t>3. Gaining new ideas for side projects. An AI agent browses GitHub, Reddit, and other websites, and creates a list of trending side projects.</t>
   </si>
 </sst>
 </file>
@@ -130,6 +139,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7188583</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81EF86BB-4339-C28C-30C5-3A0B3D316084}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="952500"/>
+          <a:ext cx="7188582" cy="4610100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,7 +513,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E376D51-2D3E-44BA-9199-BA8F83782156}">
-  <dimension ref="A1:D5"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="104.88671875" bestFit="1" customWidth="1"/>
@@ -510,7 +577,24 @@
         <v>4</v>
       </c>
     </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="31" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>